--- a/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
@@ -1,34 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56493186-AF9E-40AA-B653-F0AB8B44F915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+  <si>
+    <t>indicator_name</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>var_name</t>
+  </si>
+  <si>
+    <t>denom_var</t>
+  </si>
+  <si>
+    <t>disaggregation</t>
+  </si>
+  <si>
+    <t>multiplier</t>
+  </si>
+  <si>
+    <t>indicator_unit</t>
+  </si>
+  <si>
+    <t>Crude death rate</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>person_time</t>
+  </si>
+  <si>
+    <t>deaths/10,000/day</t>
+  </si>
+  <si>
+    <t>Under-5 mortality rate</t>
+  </si>
+  <si>
+    <t>num_died</t>
+  </si>
+  <si>
+    <t>num_died_under5</t>
+  </si>
+  <si>
+    <t>num_died_male</t>
+  </si>
+  <si>
+    <t>num_died_female</t>
+  </si>
+  <si>
+    <t>person_time_under5</t>
+  </si>
+  <si>
+    <t>person_time_male</t>
+  </si>
+  <si>
+    <t>person_time_female</t>
+  </si>
+  <si>
+    <t>Male mortality rate</t>
+  </si>
+  <si>
+    <t>Female mortality rate</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +119,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,154 +421,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>indicator_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>calculation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>var_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>denom_var</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disaggregation</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>indicator_unit</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Crude death rate</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deaths</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>person_time</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>10000</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>deaths/10,000/day</t>
-        </is>
+      <c r="G2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Under-5 mortality rate</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deaths_u5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>person_time_u5</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3">
         <v>10000</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>deaths/10,000/day</t>
-        </is>
+      <c r="G3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Infant mortality rate</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deaths_infant</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>person_time_infant</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
         <v>10000</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>deaths/10,000/day</t>
-        </is>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>10000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56493186-AF9E-40AA-B653-F0AB8B44F915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2902FEE-598D-4E27-B7E1-57CD73AFF2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,7 +427,7 @@
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>

--- a/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2902FEE-598D-4E27-B7E1-57CD73AFF2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CB6FB7-E2AD-40B2-9CFB-560B9A5B19E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>ratio</t>
   </si>
   <si>
-    <t>person_time</t>
-  </si>
-  <si>
     <t>deaths/10,000/day</t>
   </si>
   <si>
@@ -70,19 +67,22 @@
     <t>num_died_female</t>
   </si>
   <si>
-    <t>person_time_under5</t>
-  </si>
-  <si>
-    <t>person_time_male</t>
-  </si>
-  <si>
-    <t>person_time_female</t>
-  </si>
-  <si>
     <t>Male mortality rate</t>
   </si>
   <si>
     <t>Female mortality rate</t>
+  </si>
+  <si>
+    <t>linked_person_time</t>
+  </si>
+  <si>
+    <t>linked_person_time_under5</t>
+  </si>
+  <si>
+    <t>linked_person_time_male</t>
+  </si>
+  <si>
+    <t>linked_person_time_female</t>
   </si>
 </sst>
 </file>
@@ -465,76 +465,76 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>10000</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>10000</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>10000</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>10000</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_mortality_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CB6FB7-E2AD-40B2-9CFB-560B9A5B19E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE294D9-C267-41C9-9DC4-E559E130C3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
   <si>
     <t>indicator_name</t>
   </si>
@@ -83,6 +83,45 @@
   </si>
   <si>
     <t>linked_person_time_female</t>
+  </si>
+  <si>
+    <t>Trauma mortality rate</t>
+  </si>
+  <si>
+    <t>Non-Trauma mortality rate</t>
+  </si>
+  <si>
+    <t>Other Cause mortality rate</t>
+  </si>
+  <si>
+    <t>num_deaths_nontrauma</t>
+  </si>
+  <si>
+    <t>num_deaths_trauma</t>
+  </si>
+  <si>
+    <t>num_deaths_other_cause</t>
+  </si>
+  <si>
+    <t>num_deaths_current_location</t>
+  </si>
+  <si>
+    <t>num_deaths_migration</t>
+  </si>
+  <si>
+    <t>num_deaths_last_location</t>
+  </si>
+  <si>
+    <t>Current Location mortality rate</t>
+  </si>
+  <si>
+    <t>Migration mortality rate</t>
+  </si>
+  <si>
+    <t>Last Location mortality rate</t>
+  </si>
+  <si>
+    <t>stratum</t>
   </si>
 </sst>
 </file>
@@ -422,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -537,6 +576,356 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>10000</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>10000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>10000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>10000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>10000</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>10000</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>10000</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>10000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>10000</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15">
+        <v>10000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16">
+        <v>10000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17">
+        <v>10000</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18">
+        <v>10000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <v>10000</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21">
+        <v>10000</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
